--- a/templates/Apollo_Lead_Enrichment_Template.xlsx
+++ b/templates/Apollo_Lead_Enrichment_Template.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEADS" sheetId="1" r:id="Rc88595c9eb1f4e71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="2" r:id="R564d92f76a39402e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEADS" sheetId="1" r:id="Rc8ac0f5fcd2e4e09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="2" r:id="R695f698899bb4556"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -418,89 +418,100 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="7" t="str">
-        <x:v>APOLLO_ENABLED</x:v>
+        <x:v>SOURCE_SHEET_NAME</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>true</x:v>
+        <x:v>Hoja 1</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Activa o desactiva Apollo</x:v>
+        <x:v>Pestanya existent amb empreses/leads. Nomes lectura.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="7" t="str">
-        <x:v>BATCH_SIZE</x:v>
-      </x:c>
-      <x:c r="B3" s="7" t="n">
-        <x:v>10</x:v>
+        <x:v>APOLLO_ENABLED</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="str">
+        <x:v>true</x:v>
       </x:c>
       <x:c r="C3" s="7" t="str">
-        <x:v>Files processades per execucio</x:v>
+        <x:v>Activa o desactiva Apollo</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="7" t="str">
-        <x:v>MAX_CANDIDATES_PER_COMPANY</x:v>
+        <x:v>BATCH_SIZE</x:v>
       </x:c>
       <x:c r="B4" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C4" s="7" t="str">
-        <x:v>Candidats maxims retornats</x:v>
+        <x:v>Files processades per execucio</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="7" t="str">
-        <x:v>OVERWRITE_EXISTING_CONTACT_DATA</x:v>
-      </x:c>
-      <x:c r="B5" s="7" t="str">
-        <x:v>false</x:v>
+        <x:v>MAX_CANDIDATES_PER_COMPANY</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="n">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C5" s="7" t="str">
-        <x:v>Permet sobreescriure dades manuals</x:v>
+        <x:v>Candidats maxims retornats</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="7" t="str">
-        <x:v>RECHECK_AFTER_DAYS</x:v>
-      </x:c>
-      <x:c r="B6" s="7" t="n">
-        <x:v>90</x:v>
+        <x:v>OVERWRITE_EXISTING_CONTACT_DATA</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="str">
+        <x:v>false</x:v>
       </x:c>
       <x:c r="C6" s="7" t="str">
-        <x:v>Dies abans de tornar a consultar</x:v>
+        <x:v>Permet sobreescriure dades manuals</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="7" t="str">
-        <x:v>COUNTRY_DEFAULT</x:v>
-      </x:c>
-      <x:c r="B7" s="7" t="str">
-        <x:v>Spain</x:v>
+        <x:v>RECHECK_AFTER_DAYS</x:v>
+      </x:c>
+      <x:c r="B7" s="7" t="n">
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C7" s="7" t="str">
-        <x:v>Pais per defecte</x:v>
+        <x:v>Dies abans de tornar a consultar</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="7" t="str">
-        <x:v>APOLLO_API_KEY_ENV_VAR</x:v>
+        <x:v>COUNTRY_DEFAULT</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
-        <x:v>APOLLO_API_KEY</x:v>
+        <x:v>Spain</x:v>
       </x:c>
       <x:c r="C8" s="7" t="str">
-        <x:v>Variable d'entorn segura</x:v>
+        <x:v>Pais per defecte</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="7" t="str">
+        <x:v>APOLLO_API_KEY_ENV_VAR</x:v>
+      </x:c>
+      <x:c r="B9" s="7" t="str">
+        <x:v>APOLLO_API_KEY</x:v>
+      </x:c>
+      <x:c r="C9" s="7" t="str">
+        <x:v>Variable d'entorn segura</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="7" t="str">
         <x:v>WORKFLOW_VERSION</x:v>
       </x:c>
-      <x:c r="B9" s="7" t="str">
+      <x:c r="B10" s="7" t="str">
         <x:v>1.0.0</x:v>
       </x:c>
-      <x:c r="C9" s="7" t="str">
+      <x:c r="C10" s="7" t="str">
         <x:v>Versio del workflow</x:v>
       </x:c>
     </x:row>
